--- a/Train_A_Skill/Level1_Skill_Horizontal_StraightArmPull_GermanHangHold.xlsx
+++ b/Train_A_Skill/Level1_Skill_Horizontal_StraightArmPull_GermanHangHold.xlsx
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -615,12 +615,12 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>45 Degree German Hang</t>
+          <t>Split Stance German Hang</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>30s hold at ~45°</t>
+          <t>30s hold at horizontal angle</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -632,44 +632,44 @@
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>○  1</t>
+          <t>○  0</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Extension dumbbell curls</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>15 reps at 10% bodyweight</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>10–15 reps @ 5–15% BW</t>
+          <t>Ring CARS</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>TBD</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>○  1</t>
+          <t>○  0</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Weighted Stick Shoulder Dislocates</t>
+          <t>Banded shoulder rotations</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>10 reps of 5 lbs of added weight</t>
+          <t>10 reps each direction using a medium-intensity band</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>8–10 reps @ stick only → 5 lb</t>
+          <t>10 reps each direction · light–medium resistance band</t>
         </is>
       </c>
     </row>
@@ -681,17 +681,17 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Ring CARS</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
+          <t>45 Degree German Hang</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>30s hold at ~45°</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>15–30s</t>
         </is>
       </c>
     </row>
@@ -703,27 +703,73 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Banded shoulder rotations</t>
+          <t>Extension dumbbell curls</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>10 reps each direction using a medium-intensity band</t>
+          <t>15 reps at 10% bodyweight</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>10 reps each direction · light–medium resistance band</t>
+          <t>10–15 reps @ 5–15% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Weighted Stick Shoulder Dislocates</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>10 reps of 5 lbs of added weight</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>8–10 reps @ stick only → 5 lb</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Weighted Shoulder Extension Pikes</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>10 reps of 5 lbs added weight</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>8–10 reps @ stick only → 5 lb</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D13:F13"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="A5:F5"/>
+    <mergeCell ref="D12:F12"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="D7:F7"/>
@@ -736,6 +782,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -748,7 +796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -813,17 +861,17 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Weighted Shoulder Extension Pikes</t>
+          <t>Feet assisted german hang shoulder rotations</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>10 reps of 5 lbs added weight</t>
+          <t>30s hang, feet on floor</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>8–10 reps @ stick only → 5 lb</t>
+          <t>15–30s</t>
         </is>
       </c>
     </row>
@@ -835,12 +883,12 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Split Stance German Hang</t>
+          <t>Inverted Tuck Hang</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>30s hold at horizontal angle</t>
+          <t>30s hold, scapula protraction</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -893,12 +941,104 @@
         </is>
       </c>
     </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>45 Degree German Hang</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>30s hold at ~45°</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>15–30s</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Extension dumbbell curls</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>15 reps at 10% bodyweight</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>10–15 reps @ 5–15% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Weighted Stick Shoulder Dislocates</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>10 reps of 5 lbs of added weight</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>8–10 reps @ stick only → 5 lb</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Weighted Shoulder Extension Pikes</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>10 reps of 5 lbs added weight</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>8–10 reps @ stick only → 5 lb</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="13">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="A5:F5"/>
+    <mergeCell ref="D12:F12"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="D7:F7"/>
@@ -910,6 +1050,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -922,7 +1066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -987,61 +1131,61 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Feet assisted german hang shoulder rotations</t>
+          <t>Inverted hang tuck to pencil leg lift</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>30s hang, feet on floor</t>
+          <t>12 reps, 2s hold each, neutral grip</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>15–30s</t>
+          <t>6–12 reps</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>○  3</t>
+          <t>○  0</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Inverted Tuck Hang</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>30s hold, scapula protraction</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>15–30s</t>
+          <t>Ring CARS</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>TBD</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>○  3</t>
+          <t>○  0</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Inverted hang tuck to pencil leg lift</t>
+          <t>Banded shoulder rotations</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>12 reps, 2s hold each, neutral grip</t>
+          <t>10 reps each direction using a medium-intensity band</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>6–12 reps</t>
+          <t>10 reps each direction · light–medium resistance band</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1197,17 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Ring CARS</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
+          <t>45 Degree German Hang</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>30s hold at ~45°</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>15–30s</t>
         </is>
       </c>
     </row>
@@ -1075,27 +1219,73 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Banded shoulder rotations</t>
+          <t>Extension dumbbell curls</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>10 reps each direction using a medium-intensity band</t>
+          <t>15 reps at 10% bodyweight</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>10 reps each direction · light–medium resistance band</t>
+          <t>10–15 reps @ 5–15% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Weighted Stick Shoulder Dislocates</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>10 reps of 5 lbs of added weight</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>8–10 reps @ stick only → 5 lb</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Weighted Shoulder Extension Pikes</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>10 reps of 5 lbs added weight</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>8–10 reps @ stick only → 5 lb</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D13:F13"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="A5:F5"/>
+    <mergeCell ref="D12:F12"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="D7:F7"/>
@@ -1108,6 +1298,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
